--- a/propuestas/gauchos-rc-2027/Proyeccion_Royalty_Gauchos.xlsx
+++ b/propuestas/gauchos-rc-2027/Proyeccion_Royalty_Gauchos.xlsx
@@ -229,7 +229,7 @@
     <t xml:space="preserve">GAU-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaqueta cierre completo</t>
+    <t xml:space="preserve">Polerón cierre completo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidades vendidas</t>
@@ -1064,7 +1064,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
